--- a/NWspecies080122.xlsx
+++ b/NWspecies080122.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4fad9919cbe5b/Neighbourwoods/NWAnalytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{2FE53731-776B-4B2C-9475-D9F47CD357C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F605961B-8221-4E7C-BF8E-33D6A74BCC46}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="8_{2FE53731-776B-4B2C-9475-D9F47CD357C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF4987E-FBE9-4B18-BFCA-63D6C59A2C02}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'all data'!$AC$1:$AC$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$G$1:$G$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$D$1:$D$301</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9161" uniqueCount="2009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9161" uniqueCount="2010">
   <si>
     <t>ID</t>
   </si>
@@ -5399,9 +5399,6 @@
     <t>prunserr</t>
   </si>
   <si>
-    <t>prunpenn</t>
-  </si>
-  <si>
     <t>prunsarg</t>
   </si>
   <si>
@@ -6075,6 +6072,12 @@
   </si>
   <si>
     <t>popuxcan</t>
+  </si>
+  <si>
+    <t>acersacr</t>
+  </si>
+  <si>
+    <t>prunpens</t>
   </si>
 </sst>
 </file>
@@ -7011,7 +7014,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>6</v>
@@ -9983,7 +9986,7 @@
         <v>270</v>
       </c>
       <c r="G59" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H59" t="s">
         <v>21</v>
@@ -10086,7 +10089,7 @@
         <v>240</v>
       </c>
       <c r="G61" t="s">
-        <v>1783</v>
+        <v>2009</v>
       </c>
       <c r="H61" t="s">
         <v>35</v>
@@ -10139,7 +10142,7 @@
         <v>267</v>
       </c>
       <c r="G62" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H62" t="s">
         <v>21</v>
@@ -10192,7 +10195,7 @@
         <v>244</v>
       </c>
       <c r="G63" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H63" t="s">
         <v>21</v>
@@ -10286,7 +10289,7 @@
         <v>281</v>
       </c>
       <c r="G65" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H65" t="s">
         <v>40</v>
@@ -10333,7 +10336,7 @@
         <v>285</v>
       </c>
       <c r="G66" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H66" t="s">
         <v>35</v>
@@ -10386,7 +10389,7 @@
         <v>806</v>
       </c>
       <c r="G67" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H67" t="s">
         <v>21</v>
@@ -10439,7 +10442,7 @@
         <v>879</v>
       </c>
       <c r="G68" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H68" t="s">
         <v>35</v>
@@ -10492,7 +10495,7 @@
         <v>61</v>
       </c>
       <c r="G69" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H69" t="s">
         <v>21</v>
@@ -10542,7 +10545,7 @@
         <v>53</v>
       </c>
       <c r="G70" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H70" t="s">
         <v>35</v>
@@ -10595,7 +10598,7 @@
         <v>599</v>
       </c>
       <c r="G71" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H71" t="s">
         <v>35</v>
@@ -10686,7 +10689,7 @@
         <v>1036</v>
       </c>
       <c r="G73" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H73" t="s">
         <v>21</v>
@@ -10739,7 +10742,7 @@
         <v>300</v>
       </c>
       <c r="G74" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H74" t="s">
         <v>35</v>
@@ -10792,7 +10795,7 @@
         <v>306</v>
       </c>
       <c r="G75" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H75" t="s">
         <v>21</v>
@@ -10889,7 +10892,7 @@
         <v>303</v>
       </c>
       <c r="G77" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H77" t="s">
         <v>21</v>
@@ -10942,7 +10945,7 @@
         <v>313</v>
       </c>
       <c r="G78" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H78" t="s">
         <v>35</v>
@@ -10995,7 +10998,7 @@
         <v>319</v>
       </c>
       <c r="G79" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H79" t="s">
         <v>35</v>
@@ -11042,7 +11045,7 @@
         <v>316</v>
       </c>
       <c r="G80" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H80" t="s">
         <v>40</v>
@@ -11089,7 +11092,7 @@
         <v>925</v>
       </c>
       <c r="G81" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H81" t="s">
         <v>40</v>
@@ -11136,7 +11139,7 @@
         <v>329</v>
       </c>
       <c r="G82" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H82" t="s">
         <v>35</v>
@@ -11189,7 +11192,7 @@
         <v>365</v>
       </c>
       <c r="G83" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H83" t="s">
         <v>21</v>
@@ -11239,7 +11242,7 @@
         <v>339</v>
       </c>
       <c r="G84" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H84" t="s">
         <v>21</v>
@@ -11289,7 +11292,7 @@
         <v>362</v>
       </c>
       <c r="G85" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H85" t="s">
         <v>21</v>
@@ -11339,7 +11342,7 @@
         <v>343</v>
       </c>
       <c r="G86" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H86" t="s">
         <v>21</v>
@@ -11392,7 +11395,7 @@
         <v>332</v>
       </c>
       <c r="G87" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H87" t="s">
         <v>21</v>
@@ -11445,7 +11448,7 @@
         <v>358</v>
       </c>
       <c r="G88" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H88" t="s">
         <v>35</v>
@@ -11498,7 +11501,7 @@
         <v>336</v>
       </c>
       <c r="G89" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H89" t="s">
         <v>21</v>
@@ -11551,7 +11554,7 @@
         <v>347</v>
       </c>
       <c r="G90" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H90" t="s">
         <v>21</v>
@@ -11604,7 +11607,7 @@
         <v>351</v>
       </c>
       <c r="G91" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H91" t="s">
         <v>35</v>
@@ -11657,7 +11660,7 @@
         <v>355</v>
       </c>
       <c r="G92" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H92" t="s">
         <v>40</v>
@@ -11704,7 +11707,7 @@
         <v>965</v>
       </c>
       <c r="G93" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H93" t="s">
         <v>21</v>
@@ -11757,7 +11760,7 @@
         <v>969</v>
       </c>
       <c r="G94" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H94" t="s">
         <v>40</v>
@@ -11804,7 +11807,7 @@
         <v>373</v>
       </c>
       <c r="G95" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H95" t="s">
         <v>35</v>
@@ -11857,7 +11860,7 @@
         <v>323</v>
       </c>
       <c r="G96" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H96" t="s">
         <v>21</v>
@@ -11910,7 +11913,7 @@
         <v>381</v>
       </c>
       <c r="G97" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H97" t="s">
         <v>21</v>
@@ -11963,7 +11966,7 @@
         <v>385</v>
       </c>
       <c r="G98" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H98" t="s">
         <v>21</v>
@@ -12016,7 +12019,7 @@
         <v>389</v>
       </c>
       <c r="G99" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H99" t="s">
         <v>40</v>
@@ -12063,7 +12066,7 @@
         <v>377</v>
       </c>
       <c r="G100" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H100" t="s">
         <v>21</v>
@@ -12116,7 +12119,7 @@
         <v>260</v>
       </c>
       <c r="G101" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H101" t="s">
         <v>21</v>
@@ -12204,7 +12207,7 @@
         <v>394</v>
       </c>
       <c r="G103" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H103" t="s">
         <v>21</v>
@@ -12257,7 +12260,7 @@
         <v>534</v>
       </c>
       <c r="G104" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H104" t="s">
         <v>21</v>
@@ -12307,7 +12310,7 @@
         <v>404</v>
       </c>
       <c r="G105" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H105" t="s">
         <v>35</v>
@@ -12360,7 +12363,7 @@
         <v>408</v>
       </c>
       <c r="G106" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H106" t="s">
         <v>35</v>
@@ -12413,7 +12416,7 @@
         <v>419</v>
       </c>
       <c r="G107" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H107" t="s">
         <v>35</v>
@@ -12466,7 +12469,7 @@
         <v>423</v>
       </c>
       <c r="G108" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H108" t="s">
         <v>21</v>
@@ -12519,7 +12522,7 @@
         <v>430</v>
       </c>
       <c r="G109" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H109" t="s">
         <v>21</v>
@@ -12572,7 +12575,7 @@
         <v>413</v>
       </c>
       <c r="G110" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H110" t="s">
         <v>21</v>
@@ -12622,7 +12625,7 @@
         <v>416</v>
       </c>
       <c r="G111" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H111" t="s">
         <v>21</v>
@@ -12666,7 +12669,7 @@
         <v>427</v>
       </c>
       <c r="G112" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H112" t="s">
         <v>21</v>
@@ -12719,7 +12722,7 @@
         <v>433</v>
       </c>
       <c r="G113" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H113" t="s">
         <v>40</v>
@@ -12766,7 +12769,7 @@
         <v>437</v>
       </c>
       <c r="G114" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H114" t="s">
         <v>35</v>
@@ -12819,7 +12822,7 @@
         <v>441</v>
       </c>
       <c r="G115" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H115" t="s">
         <v>21</v>
@@ -12872,7 +12875,7 @@
         <v>1106</v>
       </c>
       <c r="G116" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H116" t="s">
         <v>35</v>
@@ -12960,7 +12963,7 @@
         <v>447</v>
       </c>
       <c r="G118" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H118" t="s">
         <v>35</v>
@@ -13013,7 +13016,7 @@
         <v>453</v>
       </c>
       <c r="G119" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H119" t="s">
         <v>35</v>
@@ -13066,7 +13069,7 @@
         <v>457</v>
       </c>
       <c r="G120" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H120" t="s">
         <v>35</v>
@@ -13119,7 +13122,7 @@
         <v>465</v>
       </c>
       <c r="G121" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H121" t="s">
         <v>35</v>
@@ -13172,7 +13175,7 @@
         <v>461</v>
       </c>
       <c r="G122" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H122" t="s">
         <v>35</v>
@@ -13225,7 +13228,7 @@
         <v>469</v>
       </c>
       <c r="G123" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H123" t="s">
         <v>40</v>
@@ -13272,7 +13275,7 @@
         <v>472</v>
       </c>
       <c r="G124" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H124" t="s">
         <v>40</v>
@@ -13313,7 +13316,7 @@
         <v>480</v>
       </c>
       <c r="G125" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H125" t="s">
         <v>35</v>
@@ -13357,7 +13360,7 @@
         <v>587</v>
       </c>
       <c r="G126" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H126" t="s">
         <v>40</v>
@@ -13401,7 +13404,7 @@
         <v>485</v>
       </c>
       <c r="G127" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H127" t="s">
         <v>35</v>
@@ -13454,7 +13457,7 @@
         <v>157</v>
       </c>
       <c r="G128" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H128" t="s">
         <v>21</v>
@@ -13507,7 +13510,7 @@
         <v>493</v>
       </c>
       <c r="G129" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H129" t="s">
         <v>21</v>
@@ -13560,7 +13563,7 @@
         <v>169</v>
       </c>
       <c r="G130" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H130" t="s">
         <v>21</v>
@@ -13657,7 +13660,7 @@
         <v>900</v>
       </c>
       <c r="G132" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H132" t="s">
         <v>40</v>
@@ -13707,7 +13710,7 @@
         <v>489</v>
       </c>
       <c r="G133" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H133" t="s">
         <v>35</v>
@@ -13760,7 +13763,7 @@
         <v>960</v>
       </c>
       <c r="G134" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H134" t="s">
         <v>21</v>
@@ -13804,7 +13807,7 @@
         <v>507</v>
       </c>
       <c r="G135" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H135" t="s">
         <v>21</v>
@@ -13857,7 +13860,7 @@
         <v>510</v>
       </c>
       <c r="G136" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H136" t="s">
         <v>21</v>
@@ -13901,7 +13904,7 @@
         <v>513</v>
       </c>
       <c r="G137" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H137" t="s">
         <v>21</v>
@@ -13945,7 +13948,7 @@
         <v>516</v>
       </c>
       <c r="G138" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H138" t="s">
         <v>21</v>
@@ -13995,7 +13998,7 @@
         <v>504</v>
       </c>
       <c r="G139" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H139" t="s">
         <v>40</v>
@@ -14039,7 +14042,7 @@
         <v>524</v>
       </c>
       <c r="G140" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H140" t="s">
         <v>21</v>
@@ -14092,7 +14095,7 @@
         <v>530</v>
       </c>
       <c r="G141" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H141" t="s">
         <v>21</v>
@@ -14145,7 +14148,7 @@
         <v>538</v>
       </c>
       <c r="G142" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H142" t="s">
         <v>21</v>
@@ -14198,7 +14201,7 @@
         <v>545</v>
       </c>
       <c r="G143" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H143" t="s">
         <v>21</v>
@@ -14248,7 +14251,7 @@
         <v>548</v>
       </c>
       <c r="G144" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H144" t="s">
         <v>40</v>
@@ -14292,7 +14295,7 @@
         <v>558</v>
       </c>
       <c r="G145" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H145" t="s">
         <v>21</v>
@@ -14345,7 +14348,7 @@
         <v>552</v>
       </c>
       <c r="G146" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H146" t="s">
         <v>21</v>
@@ -14398,7 +14401,7 @@
         <v>555</v>
       </c>
       <c r="G147" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H147" t="s">
         <v>40</v>
@@ -14442,7 +14445,7 @@
         <v>570</v>
       </c>
       <c r="G148" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H148" t="s">
         <v>21</v>
@@ -14495,7 +14498,7 @@
         <v>580</v>
       </c>
       <c r="G149" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H149" t="s">
         <v>21</v>
@@ -14545,7 +14548,7 @@
         <v>583</v>
       </c>
       <c r="G150" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H150" t="s">
         <v>21</v>
@@ -14595,7 +14598,7 @@
         <v>567</v>
       </c>
       <c r="G151" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H151" t="s">
         <v>21</v>
@@ -14648,7 +14651,7 @@
         <v>576</v>
       </c>
       <c r="G152" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H152" t="s">
         <v>21</v>
@@ -14701,7 +14704,7 @@
         <v>573</v>
       </c>
       <c r="G153" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H153" t="s">
         <v>40</v>
@@ -14745,7 +14748,7 @@
         <v>143</v>
       </c>
       <c r="G154" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H154" t="s">
         <v>21</v>
@@ -14798,7 +14801,7 @@
         <v>475</v>
       </c>
       <c r="G155" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H155" t="s">
         <v>21</v>
@@ -14851,7 +14854,7 @@
         <v>596</v>
       </c>
       <c r="G156" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H156" t="s">
         <v>21</v>
@@ -14945,7 +14948,7 @@
         <v>605</v>
       </c>
       <c r="G158" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H158" t="s">
         <v>21</v>
@@ -14995,7 +14998,7 @@
         <v>608</v>
       </c>
       <c r="G159" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H159" t="s">
         <v>21</v>
@@ -15048,7 +15051,7 @@
         <v>618</v>
       </c>
       <c r="G160" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H160" t="s">
         <v>21</v>
@@ -15101,7 +15104,7 @@
         <v>653</v>
       </c>
       <c r="G161" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H161" t="s">
         <v>35</v>
@@ -15151,7 +15154,7 @@
         <v>666</v>
       </c>
       <c r="G162" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H162" t="s">
         <v>35</v>
@@ -15204,7 +15207,7 @@
         <v>614</v>
       </c>
       <c r="G163" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H163" t="s">
         <v>21</v>
@@ -15257,7 +15260,7 @@
         <v>628</v>
       </c>
       <c r="G164" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H164" t="s">
         <v>21</v>
@@ -15310,7 +15313,7 @@
         <v>624</v>
       </c>
       <c r="G165" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H165" t="s">
         <v>21</v>
@@ -15363,7 +15366,7 @@
         <v>656</v>
       </c>
       <c r="G166" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H166" t="s">
         <v>35</v>
@@ -15416,7 +15419,7 @@
         <v>635</v>
       </c>
       <c r="G167" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H167" t="s">
         <v>21</v>
@@ -15469,7 +15472,7 @@
         <v>621</v>
       </c>
       <c r="G168" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H168" t="s">
         <v>21</v>
@@ -15516,7 +15519,7 @@
         <v>642</v>
       </c>
       <c r="G169" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H169" t="s">
         <v>35</v>
@@ -15569,7 +15572,7 @@
         <v>646</v>
       </c>
       <c r="G170" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H170" t="s">
         <v>35</v>
@@ -15622,7 +15625,7 @@
         <v>660</v>
       </c>
       <c r="G171" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H171" t="s">
         <v>40</v>
@@ -15666,7 +15669,7 @@
         <v>631</v>
       </c>
       <c r="G172" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H172" t="s">
         <v>35</v>
@@ -15719,7 +15722,7 @@
         <v>649</v>
       </c>
       <c r="G173" t="s">
-        <v>1866</v>
+        <v>2008</v>
       </c>
       <c r="H173" t="s">
         <v>35</v>
@@ -15772,7 +15775,7 @@
         <v>638</v>
       </c>
       <c r="G174" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H174" t="s">
         <v>21</v>
@@ -15825,7 +15828,7 @@
         <v>663</v>
       </c>
       <c r="G175" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H175" t="s">
         <v>21</v>
@@ -15875,7 +15878,7 @@
         <v>675</v>
       </c>
       <c r="G176" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H176" t="s">
         <v>35</v>
@@ -15928,7 +15931,7 @@
         <v>690</v>
       </c>
       <c r="G177" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H177" t="s">
         <v>21</v>
@@ -15978,7 +15981,7 @@
         <v>699</v>
       </c>
       <c r="G178" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H178" t="s">
         <v>21</v>
@@ -16028,7 +16031,7 @@
         <v>681</v>
       </c>
       <c r="G179" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H179" t="s">
         <v>21</v>
@@ -16081,7 +16084,7 @@
         <v>696</v>
       </c>
       <c r="G180" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H180" t="s">
         <v>21</v>
@@ -16131,7 +16134,7 @@
         <v>671</v>
       </c>
       <c r="G181" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H181" t="s">
         <v>21</v>
@@ -16184,7 +16187,7 @@
         <v>684</v>
       </c>
       <c r="G182" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H182" t="s">
         <v>35</v>
@@ -16234,7 +16237,7 @@
         <v>693</v>
       </c>
       <c r="G183" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H183" t="s">
         <v>40</v>
@@ -16278,7 +16281,7 @@
         <v>678</v>
       </c>
       <c r="G184" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H184" t="s">
         <v>21</v>
@@ -16328,7 +16331,7 @@
         <v>707</v>
       </c>
       <c r="G185" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H185" t="s">
         <v>21</v>
@@ -16378,7 +16381,7 @@
         <v>710</v>
       </c>
       <c r="G186" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H186" t="s">
         <v>35</v>
@@ -16428,7 +16431,7 @@
         <v>713</v>
       </c>
       <c r="G187" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H187" t="s">
         <v>40</v>
@@ -16472,7 +16475,7 @@
         <v>704</v>
       </c>
       <c r="G188" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H188" t="s">
         <v>21</v>
@@ -16525,7 +16528,7 @@
         <v>1029</v>
       </c>
       <c r="G189" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H189" t="s">
         <v>35</v>
@@ -16578,7 +16581,7 @@
         <v>762</v>
       </c>
       <c r="G190" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H190" t="s">
         <v>35</v>
@@ -16631,7 +16634,7 @@
         <v>740</v>
       </c>
       <c r="G191" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H191" t="s">
         <v>35</v>
@@ -16684,7 +16687,7 @@
         <v>743</v>
       </c>
       <c r="G192" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H192" t="s">
         <v>35</v>
@@ -16737,7 +16740,7 @@
         <v>749</v>
       </c>
       <c r="G193" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H193" t="s">
         <v>21</v>
@@ -16790,7 +16793,7 @@
         <v>733</v>
       </c>
       <c r="G194" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H194" t="s">
         <v>21</v>
@@ -16843,7 +16846,7 @@
         <v>730</v>
       </c>
       <c r="G195" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H195" t="s">
         <v>35</v>
@@ -16893,7 +16896,7 @@
         <v>727</v>
       </c>
       <c r="G196" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H196" t="s">
         <v>21</v>
@@ -16937,7 +16940,7 @@
         <v>746</v>
       </c>
       <c r="G197" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H197" t="s">
         <v>35</v>
@@ -16990,7 +16993,7 @@
         <v>752</v>
       </c>
       <c r="G198" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H198" t="s">
         <v>35</v>
@@ -17043,7 +17046,7 @@
         <v>724</v>
       </c>
       <c r="G199" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H199" t="s">
         <v>21</v>
@@ -17096,7 +17099,7 @@
         <v>737</v>
       </c>
       <c r="G200" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H200" t="s">
         <v>21</v>
@@ -17149,7 +17152,7 @@
         <v>756</v>
       </c>
       <c r="G201" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H201" t="s">
         <v>35</v>
@@ -17202,7 +17205,7 @@
         <v>759</v>
       </c>
       <c r="G202" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H202" t="s">
         <v>40</v>
@@ -17246,7 +17249,7 @@
         <v>721</v>
       </c>
       <c r="G203" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H203" t="s">
         <v>35</v>
@@ -17299,7 +17302,7 @@
         <v>718</v>
       </c>
       <c r="G204" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H204" t="s">
         <v>35</v>
@@ -17352,7 +17355,7 @@
         <v>920</v>
       </c>
       <c r="G205" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H205" t="s">
         <v>21</v>
@@ -17405,7 +17408,7 @@
         <v>766</v>
       </c>
       <c r="G206" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H206" t="s">
         <v>21</v>
@@ -17458,7 +17461,7 @@
         <v>771</v>
       </c>
       <c r="G207" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H207" t="s">
         <v>21</v>
@@ -17502,7 +17505,7 @@
         <v>775</v>
       </c>
       <c r="G208" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H208" t="s">
         <v>35</v>
@@ -17552,7 +17555,7 @@
         <v>779</v>
       </c>
       <c r="G209" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H209" t="s">
         <v>21</v>
@@ -17596,7 +17599,7 @@
         <v>786</v>
       </c>
       <c r="G210" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H210" t="s">
         <v>21</v>
@@ -17646,7 +17649,7 @@
         <v>783</v>
       </c>
       <c r="G211" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H211" t="s">
         <v>21</v>
@@ -17696,7 +17699,7 @@
         <v>792</v>
       </c>
       <c r="G212" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H212" t="s">
         <v>21</v>
@@ -17749,7 +17752,7 @@
         <v>789</v>
       </c>
       <c r="G213" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H213" t="s">
         <v>40</v>
@@ -17799,7 +17802,7 @@
         <v>797</v>
       </c>
       <c r="G214" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H214" t="s">
         <v>21</v>
@@ -17852,7 +17855,7 @@
         <v>802</v>
       </c>
       <c r="G215" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H215" t="s">
         <v>21</v>
@@ -17905,7 +17908,7 @@
         <v>825</v>
       </c>
       <c r="G216" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H216" t="s">
         <v>21</v>
@@ -17958,7 +17961,7 @@
         <v>810</v>
       </c>
       <c r="G217" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H217" t="s">
         <v>21</v>
@@ -18011,7 +18014,7 @@
         <v>853</v>
       </c>
       <c r="G218" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H218" t="s">
         <v>21</v>
@@ -18055,7 +18058,7 @@
         <v>814</v>
       </c>
       <c r="G219" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H219" t="s">
         <v>35</v>
@@ -18108,7 +18111,7 @@
         <v>850</v>
       </c>
       <c r="G220" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H220" t="s">
         <v>21</v>
@@ -18152,7 +18155,7 @@
         <v>822</v>
       </c>
       <c r="G221" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H221" t="s">
         <v>21</v>
@@ -18205,7 +18208,7 @@
         <v>835</v>
       </c>
       <c r="G222" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H222" t="s">
         <v>35</v>
@@ -18258,7 +18261,7 @@
         <v>828</v>
       </c>
       <c r="G223" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H223" t="s">
         <v>21</v>
@@ -18311,7 +18314,7 @@
         <v>831</v>
       </c>
       <c r="G224" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H224" t="s">
         <v>35</v>
@@ -18364,7 +18367,7 @@
         <v>846</v>
       </c>
       <c r="G225" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H225" t="s">
         <v>21</v>
@@ -18417,7 +18420,7 @@
         <v>839</v>
       </c>
       <c r="G226" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H226" t="s">
         <v>40</v>
@@ -18461,7 +18464,7 @@
         <v>818</v>
       </c>
       <c r="G227" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H227" t="s">
         <v>21</v>
@@ -18511,7 +18514,7 @@
         <v>842</v>
       </c>
       <c r="G228" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H228" t="s">
         <v>35</v>
@@ -18564,7 +18567,7 @@
         <v>864</v>
       </c>
       <c r="G229" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H229" t="s">
         <v>21</v>
@@ -18614,7 +18617,7 @@
         <v>861</v>
       </c>
       <c r="G230" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H230" t="s">
         <v>40</v>
@@ -18658,7 +18661,7 @@
         <v>222</v>
       </c>
       <c r="G231" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H231" t="s">
         <v>35</v>
@@ -18711,7 +18714,7 @@
         <v>233</v>
       </c>
       <c r="G232" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H232" t="s">
         <v>35</v>
@@ -18764,7 +18767,7 @@
         <v>230</v>
       </c>
       <c r="G233" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H233" t="s">
         <v>21</v>
@@ -18814,7 +18817,7 @@
         <v>218</v>
       </c>
       <c r="G234" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H234" t="s">
         <v>21</v>
@@ -18858,7 +18861,7 @@
         <v>875</v>
       </c>
       <c r="G235" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H235" t="s">
         <v>35</v>
@@ -18911,7 +18914,7 @@
         <v>887</v>
       </c>
       <c r="G236" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H236" t="s">
         <v>21</v>
@@ -18964,7 +18967,7 @@
         <v>897</v>
       </c>
       <c r="G237" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H237" t="s">
         <v>35</v>
@@ -19014,7 +19017,7 @@
         <v>890</v>
       </c>
       <c r="G238" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H238" t="s">
         <v>40</v>
@@ -19058,7 +19061,7 @@
         <v>871</v>
       </c>
       <c r="G239" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H239" t="s">
         <v>21</v>
@@ -19155,7 +19158,7 @@
         <v>398</v>
       </c>
       <c r="G241" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H241" t="s">
         <v>21</v>
@@ -19208,7 +19211,7 @@
         <v>903</v>
       </c>
       <c r="G242" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H242" t="s">
         <v>35</v>
@@ -19261,7 +19264,7 @@
         <v>908</v>
       </c>
       <c r="G243" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H243" t="s">
         <v>21</v>
@@ -19314,7 +19317,7 @@
         <v>932</v>
       </c>
       <c r="G244" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H244" t="s">
         <v>21</v>
@@ -19361,7 +19364,7 @@
         <v>912</v>
       </c>
       <c r="G245" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H245" t="s">
         <v>40</v>
@@ -19405,7 +19408,7 @@
         <v>916</v>
       </c>
       <c r="G246" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="H246" t="s">
         <v>21</v>
@@ -19449,7 +19452,7 @@
         <v>929</v>
       </c>
       <c r="G247" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H247" t="s">
         <v>35</v>
@@ -19502,7 +19505,7 @@
         <v>937</v>
       </c>
       <c r="G248" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H248" t="s">
         <v>21</v>
@@ -19555,7 +19558,7 @@
         <v>942</v>
       </c>
       <c r="G249" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H249" t="s">
         <v>35</v>
@@ -19608,7 +19611,7 @@
         <v>945</v>
       </c>
       <c r="G250" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H250" t="s">
         <v>40</v>
@@ -19652,7 +19655,7 @@
         <v>939</v>
       </c>
       <c r="G251" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H251" t="s">
         <v>35</v>
@@ -19705,7 +19708,7 @@
         <v>950</v>
       </c>
       <c r="G252" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H252" t="s">
         <v>21</v>
@@ -19758,7 +19761,7 @@
         <v>954</v>
       </c>
       <c r="G253" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H253" t="s">
         <v>21</v>
@@ -19846,7 +19849,7 @@
         <v>984</v>
       </c>
       <c r="G255" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H255" t="s">
         <v>35</v>
@@ -19899,7 +19902,7 @@
         <v>991</v>
       </c>
       <c r="G256" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H256" t="s">
         <v>21</v>
@@ -19952,7 +19955,7 @@
         <v>977</v>
       </c>
       <c r="G257" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H257" t="s">
         <v>21</v>
@@ -20005,7 +20008,7 @@
         <v>973</v>
       </c>
       <c r="G258" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H258" t="s">
         <v>21</v>
@@ -20058,7 +20061,7 @@
         <v>995</v>
       </c>
       <c r="G259" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H259" t="s">
         <v>35</v>
@@ -20108,7 +20111,7 @@
         <v>988</v>
       </c>
       <c r="G260" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H260" t="s">
         <v>21</v>
@@ -20158,7 +20161,7 @@
         <v>998</v>
       </c>
       <c r="G261" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H261" t="s">
         <v>40</v>
@@ -20202,7 +20205,7 @@
         <v>981</v>
       </c>
       <c r="G262" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H262" t="s">
         <v>35</v>
@@ -20293,7 +20296,7 @@
         <v>1004</v>
       </c>
       <c r="G264" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H264" t="s">
         <v>35</v>
@@ -20346,7 +20349,7 @@
         <v>1002</v>
       </c>
       <c r="G265" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H265" t="s">
         <v>40</v>
@@ -20390,7 +20393,7 @@
         <v>1009</v>
       </c>
       <c r="G266" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H266" t="s">
         <v>21</v>
@@ -20443,7 +20446,7 @@
         <v>858</v>
       </c>
       <c r="G267" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H267" t="s">
         <v>35</v>
@@ -20496,7 +20499,7 @@
         <v>541</v>
       </c>
       <c r="G268" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H268" t="s">
         <v>35</v>
@@ -20549,7 +20552,7 @@
         <v>1015</v>
       </c>
       <c r="G269" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H269" t="s">
         <v>21</v>
@@ -20602,7 +20605,7 @@
         <v>1019</v>
       </c>
       <c r="G270" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H270" t="s">
         <v>35</v>
@@ -20693,7 +20696,7 @@
         <v>1032</v>
       </c>
       <c r="G272" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H272" t="s">
         <v>40</v>
@@ -20737,7 +20740,7 @@
         <v>1047</v>
       </c>
       <c r="G273" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H273" t="s">
         <v>35</v>
@@ -20790,7 +20793,7 @@
         <v>1051</v>
       </c>
       <c r="G274" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H274" t="s">
         <v>21</v>
@@ -20843,7 +20846,7 @@
         <v>1044</v>
       </c>
       <c r="G275" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H275" t="s">
         <v>21</v>
@@ -20890,7 +20893,7 @@
         <v>1055</v>
       </c>
       <c r="G276" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H276" t="s">
         <v>40</v>
@@ -20934,7 +20937,7 @@
         <v>1026</v>
       </c>
       <c r="G277" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H277" t="s">
         <v>21</v>
@@ -21028,7 +21031,7 @@
         <v>687</v>
       </c>
       <c r="G279" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H279" t="s">
         <v>21</v>
@@ -21078,7 +21081,7 @@
         <v>1097</v>
       </c>
       <c r="G280" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H280" t="s">
         <v>21</v>
@@ -21125,7 +21128,7 @@
         <v>1081</v>
       </c>
       <c r="G281" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H281" t="s">
         <v>21</v>
@@ -21175,7 +21178,7 @@
         <v>1068</v>
       </c>
       <c r="G282" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H282" t="s">
         <v>35</v>
@@ -21222,7 +21225,7 @@
         <v>1091</v>
       </c>
       <c r="G283" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H283" t="s">
         <v>35</v>
@@ -21272,7 +21275,7 @@
         <v>1087</v>
       </c>
       <c r="G284" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H284" t="s">
         <v>21</v>
@@ -21325,7 +21328,7 @@
         <v>1078</v>
       </c>
       <c r="G285" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H285" t="s">
         <v>21</v>
@@ -21375,7 +21378,7 @@
         <v>1094</v>
       </c>
       <c r="G286" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H286" t="s">
         <v>35</v>
@@ -21422,7 +21425,7 @@
         <v>1071</v>
       </c>
       <c r="G287" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H287" t="s">
         <v>21</v>
@@ -21472,7 +21475,7 @@
         <v>1062</v>
       </c>
       <c r="G288" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H288" t="s">
         <v>21</v>
@@ -21522,7 +21525,7 @@
         <v>1074</v>
       </c>
       <c r="G289" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H289" t="s">
         <v>35</v>
@@ -21575,7 +21578,7 @@
         <v>1084</v>
       </c>
       <c r="G290" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H290" t="s">
         <v>35</v>
@@ -21669,7 +21672,7 @@
         <v>1065</v>
       </c>
       <c r="G292" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H292" t="s">
         <v>21</v>
@@ -21719,7 +21722,7 @@
         <v>1059</v>
       </c>
       <c r="G293" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H293" t="s">
         <v>21</v>
@@ -21772,7 +21775,7 @@
         <v>1103</v>
       </c>
       <c r="G294" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H294" t="s">
         <v>21</v>
@@ -21860,7 +21863,7 @@
         <v>1110</v>
       </c>
       <c r="G296" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H296" t="s">
         <v>21</v>
@@ -21910,7 +21913,7 @@
         <v>1118</v>
       </c>
       <c r="G297" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H297" t="s">
         <v>35</v>
@@ -21960,7 +21963,7 @@
         <v>1115</v>
       </c>
       <c r="G298" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H298" t="s">
         <v>21</v>
@@ -22010,7 +22013,7 @@
         <v>1121</v>
       </c>
       <c r="G299" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H299" t="s">
         <v>21</v>
@@ -22107,7 +22110,7 @@
         <v>1128</v>
       </c>
       <c r="G301" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H301" t="s">
         <v>21</v>
